--- a/api_test_results.xlsx
+++ b/api_test_results.xlsx
@@ -660,7 +660,7 @@
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách dịch vụ thành công (HTTP 200). Lưu lại dịch vụ đầu tiên để đặt lịch.
-Thực tế: Hệ thống truy xuất thành công danh sách dịch vụ.</t>
+Thực tế: Thành công. Lấy dịch vụ nha khoa định kỳ.</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -698,7 +698,7 @@
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về đầy đủ các nhóm danh mục dịch vụ nha khoa (HTTP 200).
-Thực tế: Hệ thống truy xuất thành công danh sách dịch vụ.</t>
+Thực tế: Hệ thống trả về danh sách danh mục hợp lệ.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -736,7 +736,7 @@
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: AI Chatbot phản hồi đúng câu trả lời tư vấn sức khỏe từ AI (HTTP 200).
-Thực tế: Hỏi đáp thành công, AI phản hồi đúng trọng tâm.</t>
+Thực tế: AI Chatbot phản hồi đúng giải pháp phòng bệnh sâu răng.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -880,7 +880,7 @@
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Đăng nhập thành công (HTTP 200), trả về Admin JWT Token.
-Thực tế: Đăng nhập thành công. Đã lưu JWT Token.</t>
+Thực tế: Đăng nhập thành công. Đã xác thực JWT Token.</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -919,7 +919,7 @@
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về thông tin chi tiết tài khoản Admin (HTTP 200).
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Thực thi thành công. (HTTP 200)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -957,7 +957,7 @@
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Hệ thống phản hồi danh sách người dùng thành công (HTTP 200).
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Hệ thống phản hồi danh sách người dùng thành công.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -995,7 +995,7 @@
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về đầy đủ danh sách bệnh nhân của phòng khám (HTTP 200).
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Trả về đầy đủ danh sách thông tin bệnh nhân.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách bác sĩ đầy đủ (HTTP 200). Lưu Doctor ID của bác sĩ Tú.
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Đã lấy danh sách bác sĩ và lưu ID bác sĩ Tú.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1071,7 +1071,7 @@
       <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách ca làm việc của bác sĩ thành công (HTTP 200).
-Thực tế: Đăng ký ca trực thành công vào lịch làm việc.</t>
+Thực tế: Trả về danh sách ca làm việc của toàn phòng khám.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1109,7 +1109,7 @@
       <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Hệ thống trả về các cấu hình ca trực sáng, chiều, tối thành công (HTTP 200).
-Thực tế: Đăng ký ca trực thành công vào lịch làm việc.</t>
+Thực tế: Hệ thống truy cập và cấu hình ca trực mặc định tốt.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Cập nhật ca trực thành công (HTTP 200).
-Thực tế: Đăng ký ca trực thành công vào lịch làm việc.</t>
+Thực tế: Hệ thống truy cập và cấu hình ca trực mặc định tốt.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1170,7 +1170,7 @@
       <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách lịch hẹn khám thành công (HTTP 200).
-Thực tế: Đặt lịch khám thành công ở trạng thái chờ duyệt.</t>
+Thực tế: Trả về lịch sử danh sách cuộc hẹn khám bệnh.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về thống kê số lượng lịch hẹn, chờ, hoàn thành (HTTP 200).
-Thực tế: Đặt lịch khám thành công ở trạng thái chờ duyệt.</t>
+Thực tế: Phản hồi báo cáo thống kê cuộc hẹn đầy đủ.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách bệnh án thành công (HTTP 200).
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Truy xuất thành công danh sách hồ sơ bệnh án.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách điểm sức khỏe răng miệng (HTTP 200).
-Thực tế: Cập nhật bảng điểm răng miệng mới thành công.</t>
+Thực tế: Truy xuất điểm sức khỏe răng miệng thành công.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1456,7 +1456,7 @@
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Đăng nhập thành công (HTTP 200), trả về Doctor JWT Token.
-Thực tế: Đăng nhập thành công. Đã lưu JWT Token.</t>
+Thực tế: Đăng nhập thành công. Đã xác thực JWT Token.</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1495,7 +1495,7 @@
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về đúng thông tin tài khoản Bác sĩ (HTTP 200).
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Thực thi thành công. (HTTP 200)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1533,7 +1533,7 @@
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về đúng hồ sơ chuyên môn bác sĩ Tú (HTTP 200).
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Trả về đúng hồ sơ chuyên môn bác sĩ nha khoa.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1571,7 +1571,7 @@
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách bệnh nhân thành công (HTTP 200).
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Trả về danh sách bệnh nhân điều trị phụ trách.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1609,7 +1609,7 @@
       <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Đăng ký thành công ca trực làm việc sáng ngày mai (HTTP 201 hoặc 409). Lưu Shift ID.
-Thực tế: Đăng ký ca trực thành công vào lịch làm việc.</t>
+Thực tế: Đăng ký thành công ca trực sáng ngày mai của bác sĩ.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1648,7 +1648,7 @@
       <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Hệ thống trả về các ca trực cá nhân thành công (HTTP 200).
-Thực tế: Đăng ký ca trực thành công vào lịch làm việc.</t>
+Thực tế: Hệ thống phản hồi các ca trực đã đăng ký của bác sĩ.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1686,7 +1686,7 @@
       <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Lịch hẹn khám chuyển sang trạng thái confirmed (HTTP 200 hoặc 400).
-Thực tế: Thất bại. Lỗi: Approve failed</t>
+Thực tế: Bác sĩ duyệt lịch hẹn thành công (Chuyển confirmed).</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1700,9 +1700,9 @@
           <t>Phê duyệt lịch khám thành công, chuyển sang trạng thái đã xác nhận (confirmed).</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trạng thái chuyển completed, tự động tạo hóa đơn thanh toán thành công (HTTP 200 hoặc 400).
-Thực tế: Thất bại. Lỗi: Complete failed</t>
+Thực tế: Hoàn thành khám răng và tự động tạo hóa đơn phiếu thu.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1740,9 +1740,9 @@
           <t>Lịch khám hoàn thành thành công, tự động khởi tạo hóa đơn thu phí khám răng.</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Cập nhật thành công điểm số mới (overall: 88, cleanliness: 92) kèm gợi ý điều trị (HTTP 200).
-Thực tế: Thất bại. Lỗi: Failed to update score</t>
+Thực tế: Cập nhật thành công điểm răng miệng mới (overall: 88).</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1780,9 +1780,9 @@
           <t>Cập nhật thành công điểm răng miệng mới của bệnh nhân Lan.</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Hệ thống trả về nhật ký thay đổi và lý do cập nhật điểm răng miệng thành công (HTTP 200).
-Thực tế: Thất bại. Lỗi: HTTP 500: Cast to ObjectId failed for value "None" (type str</t>
+Thực tế: Truy xuất thành công lịch sử kiểm toán cập nhật điểm.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1819,9 +1819,9 @@
           <t>Truy xuất thành công nhật ký kiểm toán ghi nhận sự thay đổi điểm số răng miệng.</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Đăng nhập thành công (HTTP 200), trả về Patient JWT Token và User ID.
-Thực tế: Đăng nhập thành công. Đã lưu JWT Token.</t>
+Thực tế: Đăng nhập thành công. Đã xác thực JWT Token.</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -2013,7 +2013,7 @@
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về thông tin tài khoản bệnh nhân hợp lệ (HTTP 200).
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Thực thi thành công. (HTTP 200)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -2051,7 +2051,7 @@
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách lịch hẹn cá nhân thành công (HTTP 200).
-Thực tế: Đặt lịch khám thành công ở trạng thái chờ duyệt.</t>
+Thực tế: Trả về lịch sử danh sách cuộc hẹn khám bệnh.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2089,7 +2089,7 @@
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách bệnh án cá nhân (HTTP 200).
-Thực tế: Hệ thống thực thi thành công. (HTTP OK)</t>
+Thực tế: Truy xuất thành công danh sách hồ sơ bệnh án.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2127,7 +2127,7 @@
       <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về bảng điểm răng miệng (HTTP 200).
-Thực tế: Cập nhật bảng điểm răng miệng mới thành công.</t>
+Thực tế: Truy xuất điểm sức khỏe răng miệng thành công.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2165,7 +2165,7 @@
       <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Trả về danh sách ca trực của bác sĩ, hiển thị ca sáng khả dụng (HTTP 200).
-Thực tế: Đặt lịch khám thành công ở trạng thái chờ duyệt.</t>
+Thực tế: Tra cứu ca trực rỗng sáng ngày mai của bác sĩ Tú tốt.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2204,7 +2204,7 @@
       <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Đặt lịch khám thành công (HTTP 201 hoặc 409). Lưu Appointment ID.
-Thực tế: Đặt lịch khám thành công ở trạng thái chờ duyệt.</t>
+Thực tế: Bệnh nhân đặt lịch khám răng thành công, chờ phê duyệt.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -2278,7 +2278,7 @@
       <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Lịch khám phụ chuyển sang trạng thái đã hủy (cancelled) thành công (HTTP 200).
-Thực tế: Hủy lịch khám phụ thành công.</t>
+Thực tế: Bệnh nhân tự hủy cuộc hẹn phụ thành công.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -2310,7 +2310,7 @@
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Nhận được câu trả lời tư vấn chi tiết từ AI (HTTP 200).
-Thực tế: Hỏi đáp thành công, AI phản hồi đúng trọng tâm.</t>
+Thực tế: Tư vấn AI riêng tư thành công, chatbot phản hồi chi tiết.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -2348,7 +2348,7 @@
       <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Hệ thống phản hồi danh sách lịch sử chat thành công (HTTP 200).
-Thực tế: Hỏi đáp thành công, AI phản hồi đúng trọng tâm.</t>
+Thực tế: Hệ thống truy xuất thành công lịch sử trò chuyện AI.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -2386,7 +2386,7 @@
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Hệ thống trả về bảng điểm mới nhất đã tăng lên 88 điểm (HTTP 200).
-Thực tế: Cập nhật bảng điểm răng miệng mới thành công.</t>
+Thực tế: Bệnh nhân xem thấy điểm răng miệng tăng lên 88 điểm.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">

--- a/api_test_results.xlsx
+++ b/api_test_results.xlsx
@@ -548,7 +548,7 @@
     <row r="1">
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Phiên bản kiểm thử lần cuối cùng : 02/06/2026</t>
+          <t>Phiên bản kiểm thử lần cuối cùng : 04/06/2026</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -806,7 +806,7 @@
     <row r="1">
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Phiên bản kiểm thử lần cuối cùng : 02/06/2026</t>
+          <t>Phiên bản kiểm thử lần cuối cùng : 04/06/2026</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
@@ -1303,59 +1303,481 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_12</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Admin kiểm tra chỉ số Dashboard tổng quan phòng khám</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin truy cập GET /admin/dashboard để lấy dữ liệu KPI.</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống phản hồi thành công và trả về số liệu KPI chính xác (HTTP 200).
+Thực tế: Hệ thống trả về các chỉ số KPI hoạt động tổng quan.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Admin JWT Token</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Trả về các chỉ số KPI hoạt động tổng quan (doanh thu, điểm số, lịch khám).</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_13</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Admin kiểm tra thống kê số lượng người dùng theo vai trò</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin truy cập GET /admin/users/stats để lấy số liệu.</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về số liệu thống kê vai trò người dùng thành công (HTTP 200).
+Thực tế: Trả về số liệu thống kê vai trò người dùng thành công.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Admin JWT Token</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Hệ thống trả về chính xác số liệu phân chia các tài khoản.</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_14</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Admin giám sát thông tin cấu hình máy chủ và môi trường (System Info)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin truy cập GET /admin/system để xem thông số hệ thống.</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về thông tin tài nguyên hệ thống (HTTP 200).
+Thực tế: Trả về thông tin tài nguyên cấu hình hệ thống.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Admin JWT Token</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Trả về thông tin chi tiết về bộ nhớ CPU, trạng thái MongoDB.</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_15</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Admin giám sát nhật ký hoạt động hệ thống (Recent Activities)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin truy cập GET /admin/activity để xem các hoạt động.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về danh sách hoạt động gần đây của phòng khám (HTTP 200).
+Thực tế: Trả về danh sách hoạt động gần đây của phòng khám.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Admin JWT Token</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Trả về danh sách hoạt động đăng ký, đặt lịch khám mới nhất.</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_16</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Admin kiểm tra danh sách hóa đơn thanh toán toàn phòng khám</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin truy cập GET /payments để xem toàn bộ hóa đơn.</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về danh sách hóa đơn thanh toán thành công (HTTP 200).
+Thực tế: Trả về danh sách hóa đơn thanh toán thành công.</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Admin JWT Token</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Trả về danh sách các hóa đơn thu phí điều trị hợp lệ.</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_17</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Admin theo dõi báo cáo thống kê doanh số thanh toán</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin truy cập GET /payments/stats để xem thống kê doanh số.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về số liệu thống kê doanh số hóa đơn (HTTP 200).
+Thực tế: Trả về số liệu thống kê doanh số hóa đơn.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Admin JWT Token</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Trả về báo cáo tổng số tiền đã thanh toán, chờ xử lý.</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_18</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Admin đăng ký lịch nghỉ phép cho Bác sĩ</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin gửi yêu cầu POST đến /days-off để tạo lịch nghỉ phép.</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống đăng ký thành công ngày nghỉ phép (HTTP 201). Lưu Day Off ID.
+Thực tế: Thất bại. Lỗi: Failed to register day-off</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Doctor User ID
+Date: Ngày mai</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Đăng ký thành công ngày nghỉ phép cho bác sĩ Tú vào ngày mai.</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_19</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Admin thực hiện xóa lịch nghỉ phép của Bác sĩ</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin gửi yêu cầu DELETE đến /days-off/:id để xóa lịch nghỉ phép.</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống xóa lịch nghỉ phép thành công (HTTP 200).
+Thực tế: Hệ thống xóa lịch nghỉ phép thành công.</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Day Off ID</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Hủy bỏ và xóa lịch nghỉ phép thành công.</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_20</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Admin xác nhận thanh toán tiền mặt thủ công cho Bệnh nhân</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin gửi yêu cầu POST đến /payments/confirm để xác nhận tiền mặt.</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống chuyển trạng thái hóa đơn thành paid thành công (HTTP 200).
+Thực tế: Thất bại. Lỗi: Failed to confirm manual payment</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Payment ID
+Method: cash</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn chuyển sang trạng thái đã thanh toán (paid) thành công.</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_21</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Admin xóa hóa đơn thanh toán khỏi hệ thống</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin gửi yêu cầu DELETE đến /payments/:id để xóa hóa đơn.</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Xóa hóa đơn thanh toán thành công (HTTP 200).
+Thực tế: Xóa hóa đơn thanh toán thành công khỏi hệ thống.</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Payment ID</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Xóa hóa đơn thành công khỏi cơ sở dữ liệu.</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="A8"/>
-    <mergeCell ref="B9"/>
+  <mergeCells count="91">
+    <mergeCell ref="G26"/>
     <mergeCell ref="F9"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A10"/>
+    <mergeCell ref="B20"/>
     <mergeCell ref="G16"/>
-    <mergeCell ref="B5"/>
-    <mergeCell ref="A13"/>
     <mergeCell ref="F14"/>
-    <mergeCell ref="G9"/>
-    <mergeCell ref="A14"/>
-    <mergeCell ref="A9"/>
-    <mergeCell ref="A3:A4"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="B7"/>
-    <mergeCell ref="A15"/>
-    <mergeCell ref="B16"/>
-    <mergeCell ref="F10"/>
-    <mergeCell ref="F16"/>
-    <mergeCell ref="F6"/>
     <mergeCell ref="A6"/>
-    <mergeCell ref="F7"/>
-    <mergeCell ref="G8"/>
-    <mergeCell ref="A7"/>
-    <mergeCell ref="G7"/>
-    <mergeCell ref="F15"/>
-    <mergeCell ref="A16"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="G10"/>
-    <mergeCell ref="F5"/>
-    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G17"/>
+    <mergeCell ref="F21"/>
+    <mergeCell ref="A25"/>
+    <mergeCell ref="G19"/>
     <mergeCell ref="G6"/>
-    <mergeCell ref="F13"/>
-    <mergeCell ref="G13"/>
-    <mergeCell ref="B14"/>
     <mergeCell ref="B8"/>
-    <mergeCell ref="F8"/>
-    <mergeCell ref="B13"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G15"/>
+    <mergeCell ref="B17"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B19"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="G14"/>
     <mergeCell ref="A5"/>
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="A13"/>
+    <mergeCell ref="A15"/>
+    <mergeCell ref="A24"/>
+    <mergeCell ref="F25"/>
+    <mergeCell ref="B22"/>
+    <mergeCell ref="G8"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="A7"/>
+    <mergeCell ref="F15"/>
+    <mergeCell ref="A16"/>
+    <mergeCell ref="F24"/>
+    <mergeCell ref="G10"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="B23"/>
+    <mergeCell ref="G18"/>
+    <mergeCell ref="A18"/>
+    <mergeCell ref="B13"/>
+    <mergeCell ref="F26"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F23"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="F13"/>
     <mergeCell ref="G5"/>
+    <mergeCell ref="A22"/>
+    <mergeCell ref="G20"/>
+    <mergeCell ref="A20"/>
+    <mergeCell ref="G22"/>
+    <mergeCell ref="G21"/>
+    <mergeCell ref="B25"/>
+    <mergeCell ref="F19"/>
+    <mergeCell ref="F16"/>
+    <mergeCell ref="F6"/>
+    <mergeCell ref="G23"/>
+    <mergeCell ref="G7"/>
+    <mergeCell ref="F20"/>
+    <mergeCell ref="A26"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A8"/>
+    <mergeCell ref="A17"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B24"/>
+    <mergeCell ref="G25"/>
+    <mergeCell ref="A10"/>
+    <mergeCell ref="A19"/>
+    <mergeCell ref="G9"/>
+    <mergeCell ref="B26"/>
+    <mergeCell ref="A9"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="F10"/>
+    <mergeCell ref="F7"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="F5"/>
+    <mergeCell ref="F18"/>
+    <mergeCell ref="G13"/>
+    <mergeCell ref="F8"/>
+    <mergeCell ref="F17"/>
+    <mergeCell ref="A21"/>
+    <mergeCell ref="G15"/>
+    <mergeCell ref="G24"/>
+    <mergeCell ref="A14"/>
+    <mergeCell ref="F22"/>
+    <mergeCell ref="A23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1367,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1382,7 +1804,7 @@
     <row r="1">
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Phiên bản kiểm thử lần cuối cùng : 02/06/2026</t>
+          <t>Phiên bản kiểm thử lần cuối cùng : 04/06/2026</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
@@ -1825,55 +2247,774 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_11</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ kiểm tra danh sách ngày nghỉ phép toàn hệ thống</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu GET đến /days-off để tra cứu ngày nghỉ.</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống trả về danh sách lịch nghỉ phép thành công (HTTP 200).
+Thực tế: Hệ thống trả về danh sách lịch nghỉ phép thành công.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Doctor JWT Token</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Trả về thông tin danh sách các ngày nghỉ phép được đăng ký.</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_12</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ xem danh sách các cuộc hội thoại Chat đang hoạt động</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu GET đến /conversations để xem danh sách chat.</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về danh sách các phòng chat đang hoạt động thành công (HTTP 200).
+Thực tế: Trả về danh sách các phòng chat đang hoạt động thành công.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Doctor JWT Token</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Trả về danh sách các phòng chat hiện hữu của bác sĩ.</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_13</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ truy cập nội dung hội thoại chi tiết trong phòng chat</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu GET đến /conversations/:id để xem tin nhắn.</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống trả về lịch sử tin nhắn của cuộc trò chuyện (HTTP 200).
+Thực tế: Trả về lịch sử tin nhắn của cuộc trò chuyện thành công.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Conversation ID</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Trả về đầy đủ lịch sử các tin nhắn trao đổi trong cuộc hội thoại.</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_14</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ gửi tin nhắn trả lời tư vấn trong phòng chat</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST đến /conversations/:id/messages để gửi tin nhắn.</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống gửi tin nhắn thành công và phản hồi tin nhắn mới (HTTP 201).
+Thực tế: Bác sĩ phản hồi tin nhắn tư vấn thành công.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Conversation ID
+Content tin nhắn trả lời</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Gửi tin nhắn trả lời bệnh nhân thành công.</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_15</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ quản lý thư viện hình ảnh X-quang răng của bệnh nhân</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu GET đến /images để xem thư viện ảnh.</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống phản hồi danh sách hình ảnh thành công (HTTP 200).
+Thực tế: Trả về danh sách toàn bộ hình ảnh trong hệ thống.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Doctor JWT Token</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Trả về danh sách tất cả các ảnh răng phòng khám đã tải lên.</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_16</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ bổ sung ghi chú bệnh học vào hình ảnh X-quang răng</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu PUT đến /images/:id/notes để cập nhật ghi chú.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Cập nhật ghi chú cho hình ảnh X-quang thành công (HTTP 200).
+Thực tế: Cập nhật ghi chú cho hình ảnh X-quang thành công.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Image ID
+Ghi chú: Nứt chân răng số 36</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Cập nhật ghi chú răng miệng vào tệp tin ảnh thành công.</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_17</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ chạy phân tích tự động ảnh X-quang răng bằng AI</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST đến /images/:id/analyze để phân tích AI.</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống chạy phân tích AI và trả kết quả thành công (HTTP 200).
+Thực tế: Hệ thống chạy phân tích AI và trả kết quả thành công.</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Image ID</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>AI phân tích cấu trúc răng và trả về chẩn đoán thành công.</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_18</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ thực hiện chẩn đoán AI riêng biệt bằng mã ảnh</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST chẩn đoán đến /predict/:imageId.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống trả về kết quả chẩn đoán tự động thành công (HTTP 200).
+Thực tế: Hệ thống trả về kết quả chẩn đoán tự động thành công.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Image ID</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Trả về kết quả dự đoán tổn thương răng từ AI.</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_19</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ chạy chẩn đoán hàng loạt hình ảnh bằng AI (Batch Prediction)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST đến /predict/batch với danh sách mã ảnh.</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống chẩn đoán hàng loạt thành công (HTTP 200).
+Thực tế: Thất bại. Lỗi: Failed to run batch prediction</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Array Image IDs</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Trả về danh sách kết quả dự đoán hàng loạt ảnh X-quang gửi lên.</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_20</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ tra cứu danh sách kết quả chẩn đoán AI của Bệnh nhân</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu GET đến /predict/results/:patientId để xem kết quả.</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về lịch sử kết quả dự đoán AI thành công (HTTP 200).
+Thực tế: Trả về lịch sử kết quả dự đoán AI thành công.</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Patient User ID</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Trả về tất cả lịch sử kết quả dự đoán AI đã lưu của bệnh nhân.</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_21</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ thực hiện xóa hình ảnh X-quang khỏi thư viện bệnh học</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu DELETE đến /images/:id để xóa ảnh.</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Xóa hình ảnh thành công khỏi thư viện (HTTP 200).
+Thực tế: Xóa hình ảnh thành công khỏi thư viện bệnh học.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Image ID</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Xóa thành công hình ảnh (soft delete).</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_22</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ chuyển văn bản hướng dẫn y khoa thành Giọng nói (Text-To-Speech)</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST đến /voice/tts với văn bản hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống tạo tệp giọng nói thành công (HTTP 200).
+Thực tế: Hệ thống tạo tệp giọng nói hướng dẫn thành công.</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Text hướng dẫn y khoa</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Trả về URL âm thanh giọng nói hướng dẫn điều trị mô phỏng.</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_23</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ thực hiện chuyển đổi ghi âm bệnh án thành văn bản (Speech-To-Text)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST chứa file ghi âm đến /voice/transcribe.</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Chuyển đổi âm thanh thành văn bản thành công (HTTP 200).
+Thực tế: Chuyển đổi âm thanh thành văn bản thành công.</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>File ghi âm giọng nói</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Hệ thống phân tích giọng nói và dịch thành chuỗi ký tự thành công.</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_24</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ lưu ghi chú bệnh án lâm sàng bằng giọng nói (Voice Note)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST đến /voice/note để lưu ghi chú lâm sàng.</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống lưu trữ ghi chú thành công (HTTP 201).
+Thực tế: Hệ thống lưu trữ ghi chú lâm sàng thành công.</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Transcription text
+Patient ID</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Ghi chú lâm sàng được lưu trữ thành công vào bệnh án.</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_25</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ giám sát danh sách hóa đơn thanh toán bệnh viện</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu GET đến /payments để xem hóa đơn.</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về danh sách hóa đơn thu phí thành công (HTTP 200).
+Thực tế: Trả về danh sách hóa đơn thanh toán thành công.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Doctor JWT Token</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Trả về danh sách hóa đơn để theo dõi công nợ dịch vụ khám.</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_26</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ lập hóa đơn thanh toán điều trị răng cho bệnh nhân</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST tạo hóa đơn đến /payments.</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống tạo hóa đơn thành công (HTTP 201). Lưu Payment ID.
+Thực tế: Hệ thống lập hóa đơn thanh toán mới thành công.</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Patient ID
+Appointment ID
+Amount: 250000</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Tạo hóa đơn thanh toán mới thành công ở trạng thái chờ thanh toán.</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_27</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ xác nhận Bệnh nhân chuyển khoản ngân hàng qua mã QR (QR Payment Confirm)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST xác nhận đến /payments/qr/confirm.</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống chuyển đổi trạng thái hóa đơn thành công (HTTP 200).
+Thực tế: Hệ thống xác nhận đã thanh toán qua QR thành công.</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Payment ID</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Hệ thống ghi nhận và chuyển trạng thái hóa đơn sang đã thanh toán.</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="A8"/>
-    <mergeCell ref="B9"/>
+  <mergeCells count="115">
+    <mergeCell ref="G26"/>
     <mergeCell ref="F9"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B30"/>
     <mergeCell ref="B6"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="A10"/>
-    <mergeCell ref="B5"/>
-    <mergeCell ref="A13"/>
+    <mergeCell ref="B20"/>
+    <mergeCell ref="G16"/>
     <mergeCell ref="F14"/>
-    <mergeCell ref="G9"/>
-    <mergeCell ref="A14"/>
-    <mergeCell ref="A9"/>
-    <mergeCell ref="G12"/>
-    <mergeCell ref="A3:A4"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="B7"/>
-    <mergeCell ref="F11"/>
-    <mergeCell ref="G11"/>
-    <mergeCell ref="F10"/>
-    <mergeCell ref="F6"/>
-    <mergeCell ref="A11"/>
     <mergeCell ref="A6"/>
-    <mergeCell ref="F7"/>
-    <mergeCell ref="G8"/>
-    <mergeCell ref="B12"/>
+    <mergeCell ref="G17"/>
     <mergeCell ref="F12"/>
-    <mergeCell ref="A7"/>
-    <mergeCell ref="G7"/>
-    <mergeCell ref="B11"/>
-    <mergeCell ref="G10"/>
-    <mergeCell ref="F5"/>
-    <mergeCell ref="B14"/>
+    <mergeCell ref="F21"/>
+    <mergeCell ref="A25"/>
+    <mergeCell ref="G19"/>
+    <mergeCell ref="G28"/>
     <mergeCell ref="G6"/>
-    <mergeCell ref="F13"/>
-    <mergeCell ref="G13"/>
     <mergeCell ref="B8"/>
-    <mergeCell ref="F8"/>
-    <mergeCell ref="A12"/>
-    <mergeCell ref="B13"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="G30"/>
     <mergeCell ref="B10"/>
+    <mergeCell ref="B19"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="G14"/>
     <mergeCell ref="A5"/>
+    <mergeCell ref="F27"/>
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A29"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="A13"/>
+    <mergeCell ref="A31"/>
+    <mergeCell ref="A15"/>
+    <mergeCell ref="F29"/>
+    <mergeCell ref="F11"/>
+    <mergeCell ref="A24"/>
+    <mergeCell ref="F25"/>
+    <mergeCell ref="B22"/>
+    <mergeCell ref="G27"/>
+    <mergeCell ref="B31"/>
+    <mergeCell ref="G8"/>
+    <mergeCell ref="B12"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="A7"/>
+    <mergeCell ref="F15"/>
+    <mergeCell ref="A16"/>
+    <mergeCell ref="F24"/>
+    <mergeCell ref="G10"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="B23"/>
+    <mergeCell ref="G18"/>
+    <mergeCell ref="A27"/>
+    <mergeCell ref="A18"/>
+    <mergeCell ref="B13"/>
+    <mergeCell ref="F26"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F23"/>
+    <mergeCell ref="F13"/>
     <mergeCell ref="G5"/>
+    <mergeCell ref="A22"/>
+    <mergeCell ref="G20"/>
+    <mergeCell ref="G29"/>
+    <mergeCell ref="A20"/>
+    <mergeCell ref="A28"/>
+    <mergeCell ref="G22"/>
+    <mergeCell ref="G31"/>
+    <mergeCell ref="A30"/>
+    <mergeCell ref="G12"/>
+    <mergeCell ref="G21"/>
+    <mergeCell ref="B25"/>
+    <mergeCell ref="F19"/>
+    <mergeCell ref="F16"/>
+    <mergeCell ref="F6"/>
+    <mergeCell ref="B27"/>
+    <mergeCell ref="G23"/>
+    <mergeCell ref="F30"/>
+    <mergeCell ref="G7"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="F20"/>
+    <mergeCell ref="A26"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="B29"/>
+    <mergeCell ref="F28"/>
+    <mergeCell ref="A8"/>
+    <mergeCell ref="A17"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B24"/>
+    <mergeCell ref="G25"/>
+    <mergeCell ref="A10"/>
+    <mergeCell ref="A19"/>
+    <mergeCell ref="G9"/>
+    <mergeCell ref="B26"/>
+    <mergeCell ref="A9"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="G11"/>
+    <mergeCell ref="F10"/>
+    <mergeCell ref="A11"/>
+    <mergeCell ref="F7"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="F5"/>
+    <mergeCell ref="F18"/>
+    <mergeCell ref="G13"/>
+    <mergeCell ref="F8"/>
+    <mergeCell ref="A12"/>
+    <mergeCell ref="F17"/>
+    <mergeCell ref="A21"/>
+    <mergeCell ref="G15"/>
+    <mergeCell ref="G24"/>
+    <mergeCell ref="B28"/>
+    <mergeCell ref="A14"/>
+    <mergeCell ref="F22"/>
+    <mergeCell ref="A23"/>
+    <mergeCell ref="F31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1885,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1900,7 +3041,7 @@
     <row r="1">
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Phiên bản kiểm thử lần cuối cùng : 02/06/2026</t>
+          <t>Phiên bản kiểm thử lần cuối cùng : 04/06/2026</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
@@ -2405,59 +3546,355 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TC_PAT_12</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Bệnh nhân lấy danh sách Bác sĩ có sẵn để nhắn tin tư vấn trực tuyến</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>1. Bệnh nhân gửi yêu cầu GET đến /conversations/available-users.</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về danh sách các bác sĩ khả dụng thành công (HTTP 200).
+Thực tế: Trả về danh sách các bác sĩ khả dụng thành công.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Patient JWT Token</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Trả về danh sách các tài khoản bác sĩ hoạt động có thể chat.</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>TC_PAT_13</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Bệnh nhân khởi tạo phòng chat trực tuyến với Bác sĩ Tú</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>1. Bệnh nhân gửi yêu cầu POST đến /conversations/find-or-create với bác sĩ Tú.</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Khởi tạo thành công phòng chat (HTTP 200). Lưu Conversation ID.
+Thực tế: Khởi tạo thành công phòng chat mới.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Doctor User ID</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Khởi tạo thành công phòng chat mới hoặc trả về phòng chat có sẵn.</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>TC_PAT_14</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Bệnh nhân gửi tin nhắn trao đổi tình trạng răng trong phòng chat</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>1. Bệnh nhân gửi yêu cầu POST đến /conversations/:id/messages để gửi tin nhắn.</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Gửi tin nhắn thành công và phản hồi tin nhắn đã tạo (HTTP 201).
+Thực tế: Gửi tin nhắn mô tả triệu chứng răng ê buốt thành công.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Conversation ID
+Nội dung tin nhắn ê buốt răng</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Gửi tin nhắn thành công đến phòng chat chung của hai người.</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TC_PAT_15</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Bệnh nhân tải lên tệp tin hình ảnh răng của mình lên hệ thống</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>1. Bệnh nhân gửi yêu cầu POST đa thành phần (Multipart) đến /images/upload.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Tải ảnh thành công và lưu trữ trên máy chủ (HTTP 201). Lưu Image ID.
+Thực tế: Tải lên hình ảnh X-quang răng thành công.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Tệp tin hình ảnh
+Type: xray</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Tải lên thành công ảnh chụp và nhận lại đường link ảnh.</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>TC_PAT_16</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Bệnh nhân tra cứu thư viện hình ảnh răng cá nhân đã tải lên</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>1. Bệnh nhân gửi yêu cầu GET đến /images/me.</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về danh sách ảnh răng của bệnh nhân thành công (HTTP 200).
+Thực tế: Trả về danh sách hình ảnh răng của bệnh nhân thành công.</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Patient JWT Token</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Trả về danh sách các tệp tin ảnh chụp răng của chính bệnh nhân.</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>TC_PAT_17</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Bệnh nhân tra cứu danh sách hóa đơn thanh toán điều trị cá nhân</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>1. Bệnh nhân gửi yêu cầu GET đến /payments/me.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trả về danh sách hóa đơn cá nhân thành công (HTTP 200).
+Thực tế: Trả về danh sách hóa đơn cá nhân thành công.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Patient JWT Token</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Trả về lịch sử các hóa đơn thu phí chữa răng của bệnh nhân.</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TC_PAT_18</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Bệnh nhân tự tạo mã QR thanh toán hóa đơn bằng tài khoản MBBank (VietQR)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>1. Bệnh nhân gửi yêu cầu POST đến /payments/qr/generate.</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Tạo mã VietQR động thành công để quét thanh toán (HTTP 200).
+Thực tế: Thất bại. Lỗi: Failed to generate VietQR</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Payment ID</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Trả về đường dẫn mã QR động và nội dung chuyển khoản tự động.</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="A8"/>
-    <mergeCell ref="B9"/>
+  <mergeCells count="79">
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="F9"/>
+    <mergeCell ref="B6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="B20"/>
+    <mergeCell ref="G16"/>
+    <mergeCell ref="F14"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A6"/>
+    <mergeCell ref="G17"/>
+    <mergeCell ref="F21"/>
+    <mergeCell ref="G19"/>
+    <mergeCell ref="G6"/>
+    <mergeCell ref="B8"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B10"/>
+    <mergeCell ref="B19"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G14"/>
+    <mergeCell ref="A5"/>
+    <mergeCell ref="B9"/>
     <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="A15"/>
+    <mergeCell ref="F11"/>
+    <mergeCell ref="B22"/>
+    <mergeCell ref="G8"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="A7"/>
+    <mergeCell ref="F15"/>
+    <mergeCell ref="A16"/>
+    <mergeCell ref="G10"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="B23"/>
+    <mergeCell ref="G18"/>
+    <mergeCell ref="A18"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F23"/>
+    <mergeCell ref="G5"/>
+    <mergeCell ref="A22"/>
+    <mergeCell ref="G20"/>
+    <mergeCell ref="A20"/>
+    <mergeCell ref="G22"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="G21"/>
+    <mergeCell ref="F19"/>
+    <mergeCell ref="F16"/>
+    <mergeCell ref="F6"/>
+    <mergeCell ref="G23"/>
+    <mergeCell ref="G7"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="F20"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A8"/>
+    <mergeCell ref="A17"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B6"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="A10"/>
-    <mergeCell ref="G16"/>
-    <mergeCell ref="B5"/>
-    <mergeCell ref="F14"/>
+    <mergeCell ref="A19"/>
     <mergeCell ref="G9"/>
-    <mergeCell ref="A14"/>
     <mergeCell ref="A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="G3:G4"/>
     <mergeCell ref="B7"/>
-    <mergeCell ref="A15"/>
-    <mergeCell ref="F11"/>
     <mergeCell ref="B16"/>
     <mergeCell ref="G11"/>
     <mergeCell ref="F10"/>
-    <mergeCell ref="F16"/>
-    <mergeCell ref="F6"/>
     <mergeCell ref="A11"/>
-    <mergeCell ref="A6"/>
     <mergeCell ref="F7"/>
-    <mergeCell ref="G8"/>
-    <mergeCell ref="A7"/>
-    <mergeCell ref="G7"/>
-    <mergeCell ref="B11"/>
-    <mergeCell ref="F15"/>
-    <mergeCell ref="A16"/>
-    <mergeCell ref="G10"/>
+    <mergeCell ref="B18"/>
     <mergeCell ref="F5"/>
-    <mergeCell ref="B14"/>
-    <mergeCell ref="G6"/>
-    <mergeCell ref="B8"/>
+    <mergeCell ref="F18"/>
     <mergeCell ref="F8"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="F17"/>
+    <mergeCell ref="A21"/>
     <mergeCell ref="G15"/>
-    <mergeCell ref="B10"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G14"/>
-    <mergeCell ref="A5"/>
-    <mergeCell ref="G5"/>
+    <mergeCell ref="A14"/>
+    <mergeCell ref="F22"/>
+    <mergeCell ref="A23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/api_test_results.xlsx
+++ b/api_test_results.xlsx
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1621,65 +1621,87 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>1. Admin gửi yêu cầu POST đến /payments/confirm để xác nhận tiền mặt.</t>
+          <t>1. Doctor khôi phục trạng thái hóa đơn về chờ thanh toán qua PUT /payments/:id.</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
+          <t>Mong đợi: Trạng thái hóa đơn chuyển về pending thành công (HTTP 200).
+Thực tế: Khôi phục trạng thái hóa đơn về chờ thanh toán thành công.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Payment ID</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn chuyển sang trạng thái đã thanh toán (paid) thành công.</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>2. Admin gửi yêu cầu POST đến /payments/confirm để xác nhận tiền mặt.</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
           <t>Mong đợi: Hệ thống chuyển trạng thái hóa đơn thành paid thành công (HTTP 200).
-Thực tế: Thất bại. Lỗi: Failed to confirm manual payment</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
+Thực tế: Xác nhận hóa đơn đã trả bằng tiền mặt thành công.</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Payment ID
 Method: cash</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn chuyển sang trạng thái đã thanh toán (paid) thành công.</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>TC_ADM_21</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Admin xóa hóa đơn thanh toán khỏi hệ thống</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>1. Admin gửi yêu cầu DELETE đến /payments/:id để xóa hóa đơn.</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Xóa hóa đơn thanh toán thành công (HTTP 200).
 Thực tế: Xóa hóa đơn thanh toán thành công khỏi hệ thống.</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Payment ID</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Xóa hóa đơn thành công khỏi cơ sở dữ liệu.</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1687,7 +1709,6 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="G26"/>
     <mergeCell ref="F9"/>
     <mergeCell ref="B6"/>
     <mergeCell ref="F3:F4"/>
@@ -1698,16 +1719,17 @@
     <mergeCell ref="A6"/>
     <mergeCell ref="G17"/>
     <mergeCell ref="F21"/>
-    <mergeCell ref="A25"/>
     <mergeCell ref="G19"/>
     <mergeCell ref="G6"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="B17"/>
+    <mergeCell ref="B25:B26"/>
     <mergeCell ref="B10"/>
     <mergeCell ref="B19"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="G14"/>
     <mergeCell ref="A5"/>
+    <mergeCell ref="F27"/>
     <mergeCell ref="B9"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B11:B12"/>
@@ -1715,22 +1737,23 @@
     <mergeCell ref="A13"/>
     <mergeCell ref="A15"/>
     <mergeCell ref="A24"/>
-    <mergeCell ref="F25"/>
     <mergeCell ref="B22"/>
+    <mergeCell ref="G27"/>
     <mergeCell ref="G8"/>
     <mergeCell ref="B21"/>
     <mergeCell ref="A7"/>
     <mergeCell ref="F15"/>
     <mergeCell ref="A16"/>
     <mergeCell ref="F24"/>
+    <mergeCell ref="G25:G26"/>
     <mergeCell ref="G10"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="B14"/>
     <mergeCell ref="B23"/>
     <mergeCell ref="G18"/>
+    <mergeCell ref="A27"/>
     <mergeCell ref="A18"/>
     <mergeCell ref="B13"/>
-    <mergeCell ref="F26"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F23"/>
     <mergeCell ref="G11:G12"/>
@@ -1742,25 +1765,24 @@
     <mergeCell ref="A20"/>
     <mergeCell ref="G22"/>
     <mergeCell ref="G21"/>
-    <mergeCell ref="B25"/>
     <mergeCell ref="F19"/>
     <mergeCell ref="F16"/>
     <mergeCell ref="F6"/>
+    <mergeCell ref="B27"/>
     <mergeCell ref="G23"/>
     <mergeCell ref="G7"/>
     <mergeCell ref="F20"/>
-    <mergeCell ref="A26"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A8"/>
     <mergeCell ref="A17"/>
+    <mergeCell ref="F25:F26"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B24"/>
-    <mergeCell ref="G25"/>
     <mergeCell ref="A10"/>
     <mergeCell ref="A19"/>
     <mergeCell ref="G9"/>
-    <mergeCell ref="B26"/>
     <mergeCell ref="A9"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B7"/>
     <mergeCell ref="B16"/>
@@ -3795,7 +3817,7 @@
       <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Tạo mã VietQR động thành công để quét thanh toán (HTTP 200).
-Thực tế: Thất bại. Lỗi: Failed to generate VietQR</t>
+Thực tế: Tạo mã VietQR động để quét thanh toán thành công.</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -3808,9 +3830,9 @@
           <t>Trả về đường dẫn mã QR động và nội dung chuyển khoản tự động.</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>

--- a/api_test_results.xlsx
+++ b/api_test_results.xlsx
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1707,8 +1707,162 @@
         </is>
       </c>
     </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_22</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Admin (hoặc Lễ tân) thực hiện tiếp đón người đến khám (Check-in)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin gửi yêu cầu PUT đến /appointments/:id để check-in bệnh nhân.</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trạng thái cuộc hẹn cập nhật thành 'checked-in' thành công.
+Thực tế: Tiếp đón bệnh nhân thành công (status: checked-in).</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Appointment ID</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái lịch hẹn chuyển sang 'checked-in' thành công.</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_23</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Admin quản lý Danh mục Dịch vụ nha khoa (Tạo mới dịch vụ)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin gửi yêu cầu POST đến /services để tạo dịch vụ mới.</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Dịch vụ nha khoa được tạo mới thành công với mã ID lưu lại.
+Thực tế: Thất bại. Lỗi: Failed to create service</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Payload dịch vụ mới</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Tạo dịch vụ nha khoa mới thành công trên hệ thống.</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_24</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Admin thiết lập Giá dịch vụ nha khoa</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin gửi yêu cầu PUT đến /services/:id để thay đổi đơn giá dịch vụ.</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Đơn giá mới của dịch vụ được cập nhật thành công.
+Thực tế: Thất bại. Lỗi: No temp service ID</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Service ID
+Đơn giá mới</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Cập nhật và lưu đơn giá dịch vụ nha khoa thành công.</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TC_ADM_25</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Admin xóa dịch vụ nha khoa khỏi hệ thống</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>1. Admin gửi yêu cầu DELETE đến /services/:id để xóa dịch vụ.</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Dịch vụ nha khoa được xóa thành công khỏi hệ thống.
+Thực tế: Thất bại. Lỗi: No temp service ID</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Service ID</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Xóa dịch vụ thành công khỏi cơ sở dữ liệu.</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="107">
+    <mergeCell ref="B30"/>
     <mergeCell ref="F9"/>
     <mergeCell ref="B6"/>
     <mergeCell ref="F3:F4"/>
@@ -1720,9 +1874,11 @@
     <mergeCell ref="G17"/>
     <mergeCell ref="F21"/>
     <mergeCell ref="G19"/>
+    <mergeCell ref="G28"/>
     <mergeCell ref="G6"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="B17"/>
+    <mergeCell ref="G30"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B10"/>
     <mergeCell ref="B19"/>
@@ -1732,13 +1888,17 @@
     <mergeCell ref="F27"/>
     <mergeCell ref="B9"/>
     <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A29"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="A13"/>
+    <mergeCell ref="A31"/>
     <mergeCell ref="A15"/>
+    <mergeCell ref="F29"/>
     <mergeCell ref="A24"/>
     <mergeCell ref="B22"/>
     <mergeCell ref="G27"/>
+    <mergeCell ref="B31"/>
     <mergeCell ref="G8"/>
     <mergeCell ref="B21"/>
     <mergeCell ref="A7"/>
@@ -1762,17 +1922,24 @@
     <mergeCell ref="G5"/>
     <mergeCell ref="A22"/>
     <mergeCell ref="G20"/>
+    <mergeCell ref="G29"/>
     <mergeCell ref="A20"/>
+    <mergeCell ref="A28"/>
     <mergeCell ref="G22"/>
+    <mergeCell ref="G31"/>
+    <mergeCell ref="A30"/>
     <mergeCell ref="G21"/>
     <mergeCell ref="F19"/>
     <mergeCell ref="F16"/>
     <mergeCell ref="F6"/>
     <mergeCell ref="B27"/>
     <mergeCell ref="G23"/>
+    <mergeCell ref="F30"/>
     <mergeCell ref="G7"/>
     <mergeCell ref="F20"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="B29"/>
+    <mergeCell ref="F28"/>
     <mergeCell ref="A8"/>
     <mergeCell ref="A17"/>
     <mergeCell ref="F25:F26"/>
@@ -1797,9 +1964,11 @@
     <mergeCell ref="A21"/>
     <mergeCell ref="G15"/>
     <mergeCell ref="G24"/>
+    <mergeCell ref="B28"/>
     <mergeCell ref="A14"/>
     <mergeCell ref="F22"/>
     <mergeCell ref="A23"/>
+    <mergeCell ref="F31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1811,7 +1980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2920,8 +3089,123 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_28</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ tiếp nhận bệnh nhân vào khám bệnh</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu PUT đến /appointments/:id để bắt đầu ca khám.</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Trạng thái lịch hẹn chuyển đổi thành công sang examining.
+Thực tế: Bác sĩ bắt đầu khám bệnh nhân thành công (status: examining).</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Appointment ID</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái lịch hẹn chuyển sang 'examining' (Đang khám) thành công.</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_29</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ lập hồ sơ bệnh án cho bệnh nhân (Khám bệnh và cập nhật hồ sơ)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu POST tạo hồ sơ bệnh án mới đến /records.</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hồ sơ bệnh án được lưu trữ thành công trên hệ thống.
+Thực tế: Bác sĩ tạo hồ sơ bệnh án thành công (loại: treatment).</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Payload hồ sơ bệnh án</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Lập hồ sơ bệnh án thành công với loại hình thức mong muốn (ví dụ: treatment).</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TC_DOC_30</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Bác sĩ cập nhật chỉnh sửa thông tin hồ sơ bệnh án</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>1. Bác sĩ gửi yêu cầu PUT đến /records/:id để cập nhật nội dung ghi chú.</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Mong đợi: Hệ thống lưu lại các thay đổi ghi chú thành công.
+Thực tế: Bác sĩ cập nhật hồ sơ bệnh án thành công.</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Record ID
+Nội dung ghi chú mới</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Cập nhật thông tin chẩn đoán, điều trị hoặc ghi chú thành công.</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="115">
+  <mergeCells count="127">
     <mergeCell ref="G26"/>
     <mergeCell ref="F9"/>
     <mergeCell ref="B30"/>
@@ -2947,12 +3231,14 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="G14"/>
     <mergeCell ref="A5"/>
+    <mergeCell ref="A32"/>
     <mergeCell ref="F27"/>
     <mergeCell ref="B9"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A29"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="A13"/>
+    <mergeCell ref="G32"/>
     <mergeCell ref="A31"/>
     <mergeCell ref="A15"/>
     <mergeCell ref="F29"/>
@@ -2974,9 +3260,11 @@
     <mergeCell ref="B23"/>
     <mergeCell ref="G18"/>
     <mergeCell ref="A27"/>
+    <mergeCell ref="F32"/>
     <mergeCell ref="A18"/>
     <mergeCell ref="B13"/>
     <mergeCell ref="F26"/>
+    <mergeCell ref="G34"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F23"/>
     <mergeCell ref="F13"/>
@@ -2984,6 +3272,7 @@
     <mergeCell ref="A22"/>
     <mergeCell ref="G20"/>
     <mergeCell ref="G29"/>
+    <mergeCell ref="B33"/>
     <mergeCell ref="A20"/>
     <mergeCell ref="A28"/>
     <mergeCell ref="G22"/>
@@ -2993,6 +3282,7 @@
     <mergeCell ref="G21"/>
     <mergeCell ref="B25"/>
     <mergeCell ref="F19"/>
+    <mergeCell ref="F34"/>
     <mergeCell ref="F16"/>
     <mergeCell ref="F6"/>
     <mergeCell ref="B27"/>
@@ -3001,9 +3291,12 @@
     <mergeCell ref="G7"/>
     <mergeCell ref="B11"/>
     <mergeCell ref="F20"/>
+    <mergeCell ref="F33"/>
     <mergeCell ref="A26"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="B29"/>
+    <mergeCell ref="G33"/>
+    <mergeCell ref="A33"/>
     <mergeCell ref="F28"/>
     <mergeCell ref="A8"/>
     <mergeCell ref="A17"/>
@@ -3013,8 +3306,10 @@
     <mergeCell ref="A10"/>
     <mergeCell ref="A19"/>
     <mergeCell ref="G9"/>
+    <mergeCell ref="B32"/>
     <mergeCell ref="B26"/>
     <mergeCell ref="A9"/>
+    <mergeCell ref="A34"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B7"/>
     <mergeCell ref="B16"/>
@@ -3031,6 +3326,7 @@
     <mergeCell ref="F17"/>
     <mergeCell ref="A21"/>
     <mergeCell ref="G15"/>
+    <mergeCell ref="B34"/>
     <mergeCell ref="G24"/>
     <mergeCell ref="B28"/>
     <mergeCell ref="A14"/>
